--- a/update-mapping-section/ig/FRServiceRequestLMCDAFHIR.xlsx
+++ b/update-mapping-section/ig/FRServiceRequestLMCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="68">
   <si>
     <t>Property</t>
   </si>
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T15:27:44+00:00</t>
+    <t>2026-08-12T09:25:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -136,70 +136,67 @@
     <t>FRCDADemandeDExamenOuDeSuivi.targetSiteCode</t>
   </si>
   <si>
+    <t>FRLMServiceRequest.priority</t>
+  </si>
+  <si>
+    <t>FRCDADemandeDExamenOuDeSuivi.priorityCode</t>
+  </si>
+  <si>
+    <t>FRLMServiceRequest.supportingInformation[x]</t>
+  </si>
+  <si>
+    <t>related-to</t>
+  </si>
+  <si>
+    <t>FRCDADemandeDExamenOuDeSuivi.entryRelationship.observation</t>
+  </si>
+  <si>
+    <t>FRLMServiceRequest.specimen</t>
+  </si>
+  <si>
+    <t>FRCDADemandeDExamenOuDeSuivi.specimen</t>
+  </si>
+  <si>
+    <t>FRLMServiceRequest.encounter</t>
+  </si>
+  <si>
+    <t>FRCDADemandeDExamenOuDeSuivi.entryRelationship.encounter</t>
+  </si>
+  <si>
+    <t>FRLMServiceRequest.occurrence[x]</t>
+  </si>
+  <si>
+    <t>FRCDADemandeDExamenOuDeSuivi.effectiveTime</t>
+  </si>
+  <si>
+    <t>FRLMServiceRequest.patientInstructions</t>
+  </si>
+  <si>
+    <t>FRCDADemandeDExamenOuDeSuivi.text</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-service-request-document</t>
+  </si>
+  <si>
+    <t>FRServiceRequestDocument</t>
+  </si>
+  <si>
+    <t>FRServiceRequestDocument.status</t>
+  </si>
+  <si>
+    <t>FRServiceRequestDocument.code</t>
+  </si>
+  <si>
+    <t>FRLMServiceRequest.quantity</t>
+  </si>
+  <si>
+    <t>FRServiceRequestDocument.quantity</t>
+  </si>
+  <si>
+    <t>FRServiceRequestDocument.bodySite</t>
+  </si>
+  <si>
     <t>FRLMServiceRequest.reason[x]</t>
-  </si>
-  <si>
-    <t>related-to</t>
-  </si>
-  <si>
-    <t>FRCDADemandeDExamenOuDeSuivi.reasonCode</t>
-  </si>
-  <si>
-    <t>FRLMServiceRequest.priority</t>
-  </si>
-  <si>
-    <t>FRCDADemandeDExamenOuDeSuivi.priorityCode</t>
-  </si>
-  <si>
-    <t>FRLMServiceRequest.supportingInformation[x]</t>
-  </si>
-  <si>
-    <t>FRCDADemandeDExamenOuDeSuivi.entryRelationship.observation</t>
-  </si>
-  <si>
-    <t>FRLMServiceRequest.specimen</t>
-  </si>
-  <si>
-    <t>FRCDADemandeDExamenOuDeSuivi.specimen</t>
-  </si>
-  <si>
-    <t>FRLMServiceRequest.encounter</t>
-  </si>
-  <si>
-    <t>FRCDADemandeDExamenOuDeSuivi.entryRelationship.encounter</t>
-  </si>
-  <si>
-    <t>FRLMServiceRequest.occurrence[x]</t>
-  </si>
-  <si>
-    <t>FRCDADemandeDExamenOuDeSuivi.effectiveTime</t>
-  </si>
-  <si>
-    <t>FRLMServiceRequest.patientInstructions</t>
-  </si>
-  <si>
-    <t>FRCDADemandeDExamenOuDeSuivi.text</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-service-request-document</t>
-  </si>
-  <si>
-    <t>FRServiceRequestDocument</t>
-  </si>
-  <si>
-    <t>FRServiceRequestDocument.status</t>
-  </si>
-  <si>
-    <t>FRServiceRequestDocument.code</t>
-  </si>
-  <si>
-    <t>FRLMServiceRequest.quantity</t>
-  </si>
-  <si>
-    <t>FRServiceRequestDocument.quantity</t>
-  </si>
-  <si>
-    <t>FRServiceRequestDocument.bodySite</t>
   </si>
   <si>
     <t>FRServiceRequestDocument.reasonCode</t>
@@ -472,7 +469,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -567,20 +564,20 @@
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s" s="2">
         <v>41</v>
-      </c>
-      <c r="D7" t="s" s="2">
-        <v>42</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s" s="2">
         <v>44</v>
@@ -593,7 +590,7 @@
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s" s="2">
         <v>46</v>
@@ -638,19 +635,6 @@
         <v>52</v>
       </c>
       <c r="E12" s="2"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D13" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="E13" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -690,7 +674,7 @@
         <v>29</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>29</v>
@@ -705,7 +689,7 @@
         <v>32</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E3" s="2"/>
     </row>
@@ -718,7 +702,7 @@
         <v>32</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E4" s="2"/>
     </row>
@@ -731,20 +715,20 @@
         <v>32</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E6" s="2"/>
     </row>
@@ -757,98 +741,98 @@
         <v>32</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E14" s="2"/>
     </row>
